--- a/KicadProject/ATS20-B-Board-BOM.xlsx
+++ b/KicadProject/ATS20-B-Board-BOM.xlsx
@@ -126,7 +126,7 @@
     <t>C1,C5,C11,C12,C13,C14,C101</t>
   </si>
   <si>
-    <t>C559769</t>
+    <t>C107185</t>
   </si>
   <si>
     <t>1u</t>
@@ -285,7 +285,7 @@
     <t>U1</t>
   </si>
   <si>
-    <t>C7236</t>
+    <t>C67473</t>
   </si>
   <si>
     <t>TL072</t>
@@ -364,7 +364,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -397,11 +397,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -478,7 +473,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -489,7 +484,7 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -507,33 +502,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -984,16 +973,16 @@
       <c r="C7" s="8">
         <v>1.0</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11" t="s">
+      <c r="H7" s="9"/>
+      <c r="I7" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="1"/>
@@ -1024,8 +1013,8 @@
       <c r="C8" s="8">
         <v>7.0</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="8" t="s">
+      <c r="D8" s="8"/>
+      <c r="E8" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -1034,8 +1023,8 @@
       <c r="G8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1064,16 +1053,16 @@
       <c r="C9" s="8">
         <v>2.0</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="8" t="s">
         <v>19</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="11" t="s">
+      <c r="H9" s="9"/>
+      <c r="I9" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="1"/>
@@ -1104,7 +1093,7 @@
       <c r="C10" s="8">
         <v>2.0</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="8" t="s">
         <v>21</v>
       </c>
@@ -1114,8 +1103,8 @@
       <c r="G10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="11"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -1144,7 +1133,7 @@
       <c r="C11" s="8">
         <v>1.0</v>
       </c>
-      <c r="D11" s="9"/>
+      <c r="D11" s="8"/>
       <c r="E11" s="8" t="s">
         <v>24</v>
       </c>
@@ -1154,8 +1143,8 @@
       <c r="G11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -1184,7 +1173,7 @@
       <c r="C12" s="8">
         <v>1.0</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="8"/>
       <c r="E12" s="8" t="s">
         <v>27</v>
       </c>
@@ -1194,8 +1183,8 @@
       <c r="G12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1224,7 +1213,7 @@
       <c r="C13" s="8">
         <v>2.0</v>
       </c>
-      <c r="D13" s="9"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="8" t="s">
         <v>30</v>
       </c>
@@ -1234,8 +1223,8 @@
       <c r="G13" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -1264,7 +1253,7 @@
       <c r="C14" s="8">
         <v>3.0</v>
       </c>
-      <c r="D14" s="9"/>
+      <c r="D14" s="8"/>
       <c r="E14" s="8" t="s">
         <v>34</v>
       </c>
@@ -1274,8 +1263,8 @@
       <c r="G14" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -1304,16 +1293,16 @@
       <c r="C15" s="8">
         <v>1.0</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
       <c r="F15" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H15" s="10"/>
-      <c r="I15" s="11" t="s">
+      <c r="H15" s="9"/>
+      <c r="I15" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="1"/>
@@ -1344,16 +1333,16 @@
       <c r="C16" s="8">
         <v>1.0</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="8" t="s">
         <v>41</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="12"/>
-      <c r="I16" s="11" t="s">
+      <c r="H16" s="10"/>
+      <c r="I16" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="1"/>
@@ -1384,16 +1373,16 @@
       <c r="C17" s="8">
         <v>3.0</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
       <c r="F17" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H17" s="10"/>
-      <c r="I17" s="11" t="s">
+      <c r="H17" s="9"/>
+      <c r="I17" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="1"/>
@@ -1424,16 +1413,16 @@
       <c r="C18" s="8">
         <v>2.0</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="10"/>
-      <c r="I18" s="11" t="s">
+      <c r="H18" s="9"/>
+      <c r="I18" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="1"/>
@@ -1464,16 +1453,16 @@
       <c r="C19" s="8">
         <v>1.0</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
       <c r="F19" s="8" t="s">
         <v>41</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="11" t="s">
+      <c r="H19" s="9"/>
+      <c r="I19" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="1"/>
@@ -1504,7 +1493,7 @@
       <c r="C20" s="8">
         <v>3.0</v>
       </c>
-      <c r="D20" s="9"/>
+      <c r="D20" s="8"/>
       <c r="E20" s="8" t="s">
         <v>52</v>
       </c>
@@ -1514,8 +1503,8 @@
       <c r="G20" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -1544,7 +1533,7 @@
       <c r="C21" s="8">
         <v>1.0</v>
       </c>
-      <c r="D21" s="9"/>
+      <c r="D21" s="8"/>
       <c r="E21" s="8" t="s">
         <v>56</v>
       </c>
@@ -1554,8 +1543,8 @@
       <c r="G21" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1584,8 +1573,8 @@
       <c r="C22" s="8">
         <v>1.0</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="13" t="s">
+      <c r="D22" s="8"/>
+      <c r="E22" s="8" t="s">
         <v>59</v>
       </c>
       <c r="F22" s="8" t="s">
@@ -1594,8 +1583,8 @@
       <c r="G22" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -1624,7 +1613,7 @@
       <c r="C23" s="8">
         <v>6.0</v>
       </c>
-      <c r="D23" s="9"/>
+      <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
         <v>62</v>
       </c>
@@ -1634,8 +1623,8 @@
       <c r="G23" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -1664,7 +1653,7 @@
       <c r="C24" s="8">
         <v>2.0</v>
       </c>
-      <c r="D24" s="9"/>
+      <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
         <v>65</v>
       </c>
@@ -1674,8 +1663,8 @@
       <c r="G24" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1704,8 +1693,8 @@
       <c r="C25" s="8">
         <v>1.0</v>
       </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="8" t="s">
+      <c r="D25" s="8"/>
+      <c r="E25" s="12" t="s">
         <v>68</v>
       </c>
       <c r="F25" s="8" t="s">
@@ -1714,8 +1703,8 @@
       <c r="G25" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1744,7 +1733,7 @@
       <c r="C26" s="8">
         <v>1.0</v>
       </c>
-      <c r="D26" s="9"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
         <v>72</v>
       </c>
@@ -1754,25 +1743,25 @@
       <c r="G26" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="15"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="15"/>
-      <c r="W26" s="15"/>
-      <c r="X26" s="15"/>
-      <c r="Y26" s="15"/>
-      <c r="Z26" s="15"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="S26" s="13"/>
+      <c r="T26" s="13"/>
+      <c r="U26" s="13"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
+      <c r="Y26" s="13"/>
+      <c r="Z26" s="13"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="7">
@@ -1784,7 +1773,7 @@
       <c r="C27" s="8">
         <v>1.0</v>
       </c>
-      <c r="D27" s="9"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
         <v>75</v>
       </c>
@@ -1794,8 +1783,8 @@
       <c r="G27" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="H27" s="14"/>
-      <c r="I27" s="10"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="9"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1824,16 +1813,16 @@
       <c r="C28" s="8">
         <v>1.0</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
       <c r="F28" s="8" t="s">
         <v>79</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="14"/>
-      <c r="I28" s="11" t="s">
+      <c r="H28" s="11"/>
+      <c r="I28" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J28" s="1"/>
@@ -1864,7 +1853,7 @@
       <c r="C29" s="8">
         <v>1.0</v>
       </c>
-      <c r="D29" s="9"/>
+      <c r="D29" s="8"/>
       <c r="E29" s="8" t="s">
         <v>81</v>
       </c>
@@ -1874,8 +1863,8 @@
       <c r="G29" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -1904,7 +1893,7 @@
       <c r="C30" s="8">
         <v>1.0</v>
       </c>
-      <c r="D30" s="9"/>
+      <c r="D30" s="8"/>
       <c r="E30" s="8" t="s">
         <v>84</v>
       </c>
@@ -1914,8 +1903,8 @@
       <c r="G30" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -1944,7 +1933,7 @@
       <c r="C31" s="8">
         <v>1.0</v>
       </c>
-      <c r="D31" s="9"/>
+      <c r="D31" s="8"/>
       <c r="E31" s="8" t="s">
         <v>88</v>
       </c>
@@ -1954,8 +1943,8 @@
       <c r="G31" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -1976,12 +1965,12 @@
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="7"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -2116,7 +2105,7 @@
       <c r="Z37" s="1"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="15" t="s">
         <v>91</v>
       </c>
       <c r="J38" s="1"/>
@@ -2138,15 +2127,15 @@
       <c r="Z38" s="1"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -2166,7 +2155,7 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="16" t="s">
         <v>92</v>
       </c>
       <c r="J40" s="1"/>
@@ -2272,11 +2261,11 @@
       <c r="Z43" s="1"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="19"/>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -2298,12 +2287,12 @@
       <c r="Z44" s="1"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="19"/>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -2325,11 +2314,11 @@
       <c r="Z45" s="1"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="19"/>
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -2351,12 +2340,12 @@
       <c r="Z46" s="1"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="19"/>
-      <c r="B47" s="16"/>
-      <c r="C47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -2378,12 +2367,12 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="19"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -2405,12 +2394,12 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="19"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -2432,12 +2421,12 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="19"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -2459,12 +2448,12 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="19"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
+      <c r="A51" s="17"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -2486,11 +2475,11 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="19"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
+      <c r="A52" s="17"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -2512,11 +2501,11 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="19"/>
-      <c r="B53" s="16"/>
-      <c r="C53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -2538,11 +2527,11 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="19"/>
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
+      <c r="A54" s="17"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -2564,11 +2553,11 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="19"/>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -2590,11 +2579,11 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="19"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -2616,12 +2605,12 @@
       <c r="Z56" s="1"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="19"/>
-      <c r="B57" s="16"/>
-      <c r="C57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
+      <c r="A57" s="17"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -2643,12 +2632,12 @@
       <c r="Z57" s="1"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="19"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
+      <c r="A58" s="17"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -2670,11 +2659,11 @@
       <c r="Z58" s="1"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="19"/>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -2696,12 +2685,12 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="19"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
@@ -2723,12 +2712,12 @@
       <c r="Z60" s="1"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="19"/>
-      <c r="B61" s="16"/>
-      <c r="C61" s="16"/>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16"/>
+      <c r="A61" s="17"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -2750,12 +2739,12 @@
       <c r="Z61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="19"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="14"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -2777,12 +2766,12 @@
       <c r="Z62" s="1"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="19"/>
-      <c r="B63" s="16"/>
-      <c r="C63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16"/>
+      <c r="A63" s="17"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -2804,12 +2793,12 @@
       <c r="Z63" s="1"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="19"/>
-      <c r="B64" s="16"/>
-      <c r="C64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
@@ -2831,11 +2820,11 @@
       <c r="Z64" s="1"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="19"/>
-      <c r="B65" s="16"/>
-      <c r="C65" s="16"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
+      <c r="A65" s="17"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
@@ -2857,12 +2846,12 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="19"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
+      <c r="A66" s="17"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -2884,12 +2873,12 @@
       <c r="Z66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="19"/>
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
@@ -2911,12 +2900,12 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="19"/>
-      <c r="B68" s="16"/>
-      <c r="C68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="16"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="14"/>
+      <c r="C68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
